--- a/human_resources_forms/029_payroll_transparency_perception_survey--human_resources_forms.xlsx
+++ b/human_resources_forms/029_payroll_transparency_perception_survey--human_resources_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -442,7 +442,7 @@
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="23" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
     <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -975,7 +975,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Job Title</t>
+          <t>Job Title Supervisor</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -998,7 +998,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Job Title</t>
+          <t>Job Title Department</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -1021,7 +1021,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Supervisor Email</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>Supervisor Phone</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1067,7 +1067,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Department</t>
+          <t>Supervisor Department</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1134,12 +1134,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:C22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1167,12 +1167,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1201,29 +1201,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>pay_period_choices</t>
+          <t>pay_frequency_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>option4</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>option4</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1235,12 +1235,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>option5</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>option5</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1252,46 +1252,46 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>option6</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>option6</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>pay_frequency_choices</t>
+          <t>benefits_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>option7</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>option7</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>pay_frequency_choices</t>
+          <t>benefits_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>option8</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>option8</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1303,46 +1303,46 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>option9</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>option9</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>benefits_choices</t>
+          <t>benefits_frequency_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>option10</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>option10</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>benefits_choices</t>
+          <t>benefits_frequency_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>option11</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>option11</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1354,46 +1354,46 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>option12</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>option12</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>benefits_frequency_choices</t>
+          <t>communication_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>option13</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>option13</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>benefits_frequency_choices</t>
+          <t>communication_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>option14</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>option14</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1405,46 +1405,46 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>option15</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>option15</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>communication_choices</t>
+          <t>trust_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>option16</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>option16</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>communication_choices</t>
+          <t>trust_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>option17</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>option17</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1456,46 +1456,46 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>option18</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>option18</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>trust_choices</t>
+          <t>transparency_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>option19</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>option19</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>trust_choices</t>
+          <t>transparency_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>option20</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>option20</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1507,46 +1507,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>option21</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>option21</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>transparency_choices</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>option22</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>option22</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>transparency_choices</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>option23</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>option23</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
